--- a/master-db/renault.xlsx
+++ b/master-db/renault.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kang1\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kang1\Documents\GitHub\ildeung-battery-v1\master-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9BF6B9F-0C62-4D4F-9AEB-0605CF9E39C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E26550E-B8E7-46CB-935C-81A2D60FE3AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4710" yWindow="3360" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="르노" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="116">
   <si>
     <t>제조사</t>
   </si>
@@ -59,33 +59,21 @@
     <t>가솔린</t>
   </si>
   <si>
-    <t>SM3 (02/09~05/08) 가솔린</t>
-  </si>
-  <si>
     <t>완료</t>
   </si>
   <si>
     <t>05/08~09/06</t>
   </si>
   <si>
-    <t>SM3 뉴제너레이션 (05/08~09/06) 가솔린</t>
-  </si>
-  <si>
     <t>DF80L</t>
   </si>
   <si>
     <t>09/06~11/03</t>
   </si>
   <si>
-    <t>SM3 CE (09/06~11/03) 가솔린</t>
-  </si>
-  <si>
     <t>09/07~14/04</t>
   </si>
   <si>
-    <t>뉴SM3신형 (09/07~14/04) 가솔린</t>
-  </si>
-  <si>
     <t>DIN74L</t>
   </si>
   <si>
@@ -95,21 +83,12 @@
     <t>전기차</t>
   </si>
   <si>
-    <t>SM3 Z.E 전기차 시동용 (13년~)</t>
-  </si>
-  <si>
     <t>14/04~20/01</t>
   </si>
   <si>
-    <t>SM3네오 (14/04~20/01) 가솔린</t>
-  </si>
-  <si>
     <t>디젤</t>
   </si>
   <si>
-    <t>SM3네오 (14/04~20/01) 디젤</t>
-  </si>
-  <si>
     <t>AGM70</t>
   </si>
   <si>
@@ -122,54 +101,24 @@
     <t>가솔린, LPG</t>
   </si>
   <si>
-    <t>SM5 (98/03~05/01) 가솔린, LPG</t>
-  </si>
-  <si>
     <t>05/01~07/07</t>
   </si>
   <si>
-    <t>뉴SM5 (05/01~07/07) 가솔린, LPG</t>
-  </si>
-  <si>
     <t>07/07~10/11</t>
   </si>
   <si>
-    <t>SM5뉴임프레션 (07/07~10/11) 가솔린, LPG</t>
-  </si>
-  <si>
     <t>10/01~12/11</t>
   </si>
   <si>
-    <t>뉴SM5신형 (10/01~12/11) 가솔린</t>
-  </si>
-  <si>
     <t>LPG</t>
   </si>
   <si>
-    <t>뉴SM5신형 (10/01~12/11) LPG</t>
-  </si>
-  <si>
     <t>12/11~15/01</t>
   </si>
   <si>
-    <t>뉴SM5플래티넘 (12/11~15/01) 가솔린, LPG</t>
-  </si>
-  <si>
-    <t>뉴SM5플래티넘 (12/11~15/01) 디젤</t>
-  </si>
-  <si>
     <t>15/01~19/12</t>
   </si>
   <si>
-    <t>SM5노바 (15/01~19/12) 가솔린</t>
-  </si>
-  <si>
-    <t>SM5노바 (15/01~19/12) LPG</t>
-  </si>
-  <si>
-    <t>SM5노바 (15/01~19/12) 디젤</t>
-  </si>
-  <si>
     <t>SM6</t>
   </si>
   <si>
@@ -179,180 +128,84 @@
     <t>가솔린, 디젤</t>
   </si>
   <si>
-    <t>SM6 (16/03~20/07) 가솔린, 디젤</t>
-  </si>
-  <si>
-    <t>SM6 (16/03~20/07) LPG</t>
-  </si>
-  <si>
     <t>20/07~</t>
   </si>
   <si>
-    <t>더뉴SM6 (20/07~) 가솔린</t>
-  </si>
-  <si>
-    <t>더뉴SM6 (20/07~) LPG</t>
-  </si>
-  <si>
     <t>SM7</t>
   </si>
   <si>
     <t>04/12~08/01</t>
   </si>
   <si>
-    <t>SM7 (04/12~08/01) 가솔린</t>
-  </si>
-  <si>
     <t>08/01~11/08</t>
   </si>
   <si>
-    <t>SM7뉴아트 (08/01~11/08) 가솔린</t>
-  </si>
-  <si>
     <t>11/08~14/09</t>
   </si>
   <si>
-    <t>올뉴SM7 (11/08~14/09) 가솔린</t>
-  </si>
-  <si>
     <t>DIN100L</t>
   </si>
   <si>
     <t>오토스탑</t>
   </si>
   <si>
-    <t>올뉴SM7 오토스탑 (11/08~14/09)</t>
-  </si>
-  <si>
     <t>AGM95</t>
   </si>
   <si>
-    <t>올뉴SM7 (11/08~14/09) LPG</t>
-  </si>
-  <si>
     <t>14/09~20/01</t>
   </si>
   <si>
-    <t>뉴SM7노바 (14/09~20/01) 가솔린</t>
-  </si>
-  <si>
-    <t>뉴SM7노바 오토스탑 (14/09~20/01)</t>
-  </si>
-  <si>
-    <t>뉴SM7노바 (14/09~20/01) LPG</t>
-  </si>
-  <si>
     <t>QM3</t>
   </si>
   <si>
     <t>13/11~17/07</t>
   </si>
   <si>
-    <t>QM3 (13/11~17/07) 디젤</t>
-  </si>
-  <si>
-    <t>뉴QM3 (13/11~17/07) 디젤</t>
-  </si>
-  <si>
     <t>QM5</t>
   </si>
   <si>
     <t>07/12~11/06</t>
   </si>
   <si>
-    <t>QM5 (07/12~11/06) 가솔린, 디젤</t>
-  </si>
-  <si>
     <t>11/06~14/01</t>
   </si>
   <si>
-    <t>뉴QM5 (11/06~14/01) 가솔린</t>
-  </si>
-  <si>
-    <t>뉴QM5 (11/06~14/01) 디젤</t>
-  </si>
-  <si>
     <t>14/01~16/09</t>
   </si>
   <si>
-    <t>QM5네오 (14/01~16/09) 가솔린</t>
-  </si>
-  <si>
-    <t>QM5네오 (14/01~16/09) 디젤</t>
-  </si>
-  <si>
     <t>QM6</t>
   </si>
   <si>
     <t>16/09~19/06</t>
   </si>
   <si>
-    <t>QM6 (16/09~19/06) 가솔린</t>
-  </si>
-  <si>
-    <t>QM6 (16/09~19/06) 디젤</t>
-  </si>
-  <si>
     <t>19/06~20/11</t>
   </si>
   <si>
-    <t>더뉴QM6 (19/06~20/11) 가솔린</t>
-  </si>
-  <si>
-    <t>더뉴QM6 (19/06~20/11) 디젤</t>
-  </si>
-  <si>
-    <t>더뉴QM6 (19/06~20/11) LPG</t>
-  </si>
-  <si>
     <t>20/11~</t>
   </si>
   <si>
-    <t>뉴QM6 (20/11~) 가솔린</t>
-  </si>
-  <si>
-    <t>뉴QM6 (20/11~) 디젤</t>
-  </si>
-  <si>
-    <t>뉴QM6 (20/11~) LPG</t>
-  </si>
-  <si>
     <t>XM3</t>
   </si>
   <si>
     <t>20년~</t>
   </si>
   <si>
-    <t>XM3 (20년~)</t>
-  </si>
-  <si>
     <t>마스터</t>
   </si>
   <si>
     <t>18년~</t>
   </si>
   <si>
-    <t>마스터 (18년~) 디젤</t>
-  </si>
-  <si>
     <t>캡처</t>
   </si>
   <si>
-    <t>캡처 (20년~) 가솔린</t>
-  </si>
-  <si>
     <t>AGM60</t>
   </si>
   <si>
-    <t>캡처 (20년~) 디젤</t>
-  </si>
-  <si>
     <t>클리오</t>
   </si>
   <si>
-    <t>클리오 (18년~) 디젤</t>
-  </si>
-  <si>
     <t>르노 차량 배터리 DB</t>
   </si>
   <si>
@@ -412,6 +265,743 @@
   </si>
   <si>
     <t xml:space="preserve">AGM60 </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SM3D</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SM3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뉴제너레이션</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SM3 CE </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뉴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>SM3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>신형</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SM3 Z.E </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>SM3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>네오</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SM5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뉴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">SM5 </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>SM5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뉴임프레션</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뉴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>SM5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>신형</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뉴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>SM5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>신형</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뉴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>SM5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>플래티넘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뉴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>SM5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>플래티넘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>SM5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>노바</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SM6 </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>더뉴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>SM6</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>더뉴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">SM6 </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SM7</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>SM7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뉴아트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>올뉴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">SM7 </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>올뉴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">SM7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뉴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>SM7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>노바</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뉴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>SM7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>노바</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>QM3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뉴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>QM3</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">QM5 </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뉴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>QM5</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>QM5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>네오</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>QM5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>네오</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">QM6 </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>더뉴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>QM6</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>더뉴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">QM6 </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뉴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>QM6</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>뉴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">QM6 </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>XM3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마스터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>캡처</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>클리오</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t/>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -419,7 +1009,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -442,6 +1032,18 @@
     <font>
       <sz val="8"/>
       <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -472,7 +1074,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -481,6 +1083,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -716,16 +1321,16 @@
         <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -736,20 +1341,20 @@
         <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -760,22 +1365,22 @@
         <v>9</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -786,20 +1391,20 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>20</v>
+      <c r="E5" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -810,20 +1415,20 @@
         <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -834,22 +1439,22 @@
         <v>9</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>118</v>
+        <v>69</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -860,20 +1465,20 @@
         <v>9</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -881,23 +1486,23 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -905,47 +1510,47 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="28.5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>37</v>
+        <v>86</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -953,25 +1558,25 @@
         <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>39</v>
+      <c r="E12" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>121</v>
+        <v>72</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -979,49 +1584,49 @@
         <v>8</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>41</v>
+        <v>29</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="28.5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="D14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>43</v>
+        <v>25</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>89</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1029,25 +1634,25 @@
         <v>8</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="D15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>44</v>
+        <v>21</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1055,25 +1660,25 @@
         <v>8</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1081,23 +1686,23 @@
         <v>8</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1105,25 +1710,25 @@
         <v>8</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1131,23 +1736,23 @@
         <v>8</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1155,23 +1760,23 @@
         <v>8</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1179,23 +1784,23 @@
         <v>8</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>55</v>
+      <c r="E21" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1203,23 +1808,23 @@
         <v>8</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>56</v>
+        <v>29</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1227,23 +1832,23 @@
         <v>8</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1251,23 +1856,23 @@
         <v>8</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1275,23 +1880,23 @@
         <v>8</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>63</v>
+      <c r="E25" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1299,23 +1904,23 @@
         <v>8</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>66</v>
+        <v>41</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1323,25 +1928,25 @@
         <v>8</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>68</v>
+        <v>29</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>121</v>
+        <v>72</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1349,23 +1954,23 @@
         <v>8</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>70</v>
+      <c r="E28" s="4" t="s">
+        <v>99</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1373,23 +1978,23 @@
         <v>8</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>71</v>
+        <v>41</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>99</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1397,23 +2002,23 @@
         <v>8</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>72</v>
+        <v>29</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>100</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1421,23 +2026,23 @@
         <v>8</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1445,23 +2050,23 @@
         <v>8</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>76</v>
+        <v>21</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>102</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1469,23 +2074,23 @@
         <v>8</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1493,23 +2098,23 @@
         <v>8</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>81</v>
+      <c r="E34" s="4" t="s">
+        <v>104</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1517,23 +2122,23 @@
         <v>8</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>82</v>
+        <v>21</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>104</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1541,23 +2146,23 @@
         <v>8</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1565,23 +2170,23 @@
         <v>8</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G37" s="2"/>
       <c r="H37" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1589,25 +2194,25 @@
         <v>8</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1615,23 +2220,23 @@
         <v>8</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1639,25 +2244,25 @@
         <v>8</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>91</v>
+      <c r="E40" s="4" t="s">
+        <v>108</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1665,23 +2270,23 @@
         <v>8</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>92</v>
+        <v>21</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>109</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1689,23 +2294,23 @@
         <v>8</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>93</v>
+        <v>29</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>108</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G42" s="2"/>
       <c r="H42" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1713,25 +2318,25 @@
         <v>8</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>95</v>
+      <c r="E43" s="4" t="s">
+        <v>110</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1739,23 +2344,23 @@
         <v>8</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>96</v>
+        <v>21</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>111</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1763,23 +2368,23 @@
         <v>8</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>97</v>
+        <v>29</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>111</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G45" s="2"/>
       <c r="H45" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1787,23 +2392,23 @@
         <v>8</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="2" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>126</v>
+        <v>77</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -1811,23 +2416,23 @@
         <v>8</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>101</v>
+        <v>56</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>103</v>
+        <v>21</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>113</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1835,23 +2440,23 @@
         <v>8</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E48" s="2" t="s">
-        <v>105</v>
+      <c r="E48" s="4" t="s">
+        <v>114</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>106</v>
+        <v>59</v>
       </c>
       <c r="G48" s="2"/>
       <c r="H48" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -1859,23 +2464,23 @@
         <v>8</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>99</v>
+        <v>55</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>107</v>
+        <v>21</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>114</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -1883,23 +2488,23 @@
         <v>8</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>109</v>
+        <v>21</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>115</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1926,32 +2531,32 @@
   <sheetData>
     <row r="1" spans="1:1" ht="20.25">
       <c r="A1" s="3" t="s">
-        <v>110</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>111</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>112</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>113</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>114</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>115</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
